--- a/data/trans_orig/IP11A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP11A_R-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -841,42 +841,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>13243</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>12888</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>13243</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -954,52 +954,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>13243</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13243</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13243</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>12888</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>12888</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>12888</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>13243</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>13243</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>13243</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1179,47 +1179,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13703</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>7045</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>13703</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>13703</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>13703</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>13703</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>7045</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>7045</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>7045</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>13703</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>13703</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>13703</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,107 +1409,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2714</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>30,51%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>487</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2732</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>2478</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>30,71%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2588</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8408</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6181</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8895</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>69,49%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>6332</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>8408</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>6163</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>8895</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,52%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>12749</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8895</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8895</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8895</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>6332</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>6332</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>6332</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>8895</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>8895</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>8895</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,107 +1752,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4064</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,53%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>38,03%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3458</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,53%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4090</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>6,79%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>32,37%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4458</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9346</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6621</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10685</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,47%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>61,97%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>9039</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>9346</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>7227</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>10685</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>87,47%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15266</t>
+          <t>15634</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10685</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>10685</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>10685</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>9039</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>9039</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>9039</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>10685</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>10685</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>10685</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,92 +2095,92 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4975</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,69%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1826</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4861</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>10,45%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>488</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>44699</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>41550</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>46040</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>89,31%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>35304</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>44699</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>41664</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>46044</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>76730</t>
+          <t>76926</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>81344</t>
+          <t>81341</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46525</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46525</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46525</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>35304</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>35304</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>35304</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46525</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46525</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46525</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2783,47 +2783,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16370</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>9073</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16370</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16370</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16370</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16370</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>9073</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>9073</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>9073</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>16370</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>16370</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>16370</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,107 +3013,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>710</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3494</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3813</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,31%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,3%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>17,79%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3752</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>710</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3549</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -3126,74 +3126,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19495</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>20721</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17937</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>17618</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>21431</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,69%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,7%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>82,21%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>19495</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>59</t>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37377</t>
+          <t>37174</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>19495</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19495</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>19495</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>21431</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>21431</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>21431</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>19495</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>19495</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>19495</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,107 +3356,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,14%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>628</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3467</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3082</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>19,11%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2783</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17513</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15031</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>18141</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,54%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>82,86%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>8498</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>17513</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>14674</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>18141</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,54%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23856</t>
+          <t>23557</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18141</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18141</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18141</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>8498</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>8498</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>8498</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>18141</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>18141</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>18141</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,107 +3699,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6823</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>35,22%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1893</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6289</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>6534</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>32,46%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>6119</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17478</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12548</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>19371</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>64,78%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>12709</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>17478</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>13082</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>19371</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,23%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25961</t>
+          <t>25546</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>19371</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>19371</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>19371</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>12709</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>12709</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>12709</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>19371</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>19371</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>19371</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2521</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7305</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>710</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4234</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3544</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2521</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7867</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>713</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -4155,74 +4155,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>70856</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>66072</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>72751</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,04%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>51002</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>47478</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>48168</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>51712</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,63%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,81%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>93,15%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>70856</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>65510</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>72745</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,56%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>89,28%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>176</t>
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>116766</t>
+          <t>116944</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124377</t>
+          <t>124376</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>73377</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>73377</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>73377</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>51712</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>51712</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>51712</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>73377</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>73377</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>73377</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,107 +4617,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3595</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3659</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>19,14%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>51,39%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>52,3%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4355</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4137</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>7,89%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9981</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>5657</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3401</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3337</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>6996</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>80,86%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>48,61%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>47,7%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>9981</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>21</t>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12839</t>
+          <t>12621</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9981</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9981</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9981</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>6996</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>6996</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>6996</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>9981</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>9981</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9981</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,107 +4960,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>640</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2646</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2649</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,15%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>29,55%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>29,58%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4039</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3180</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -5073,74 +5073,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11082</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>8315</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6309</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>6306</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>8955</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>92,85%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70,45%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>70,42%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>11082</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>30</t>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16857</t>
+          <t>15998</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>11082</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>11082</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>11082</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>8955</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>8955</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>8955</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>11082</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>11082</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>11082</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,107 +5303,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,45%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>38,25%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2922</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>7,45%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3273</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>37,02%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2704</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7304</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4873</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7892</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,55%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>61,75%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>4465</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>7304</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>4970</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>7892</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>92,55%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9652</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7892</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7892</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7892</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>4465</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>4465</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>4465</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>7892</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>7892</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>7892</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5651,102 +5651,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3572</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,06%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>30,35%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>772</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2343</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2264</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>26,13%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>79,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>76,65%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1485</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3912</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4587</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>10,09%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>33,24%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1485</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4461</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>10,09%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>31,16%</t>
         </is>
       </c>
     </row>
@@ -5759,74 +5759,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11056</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8197</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>11769</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,94%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>69,65%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2182</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>611</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>2954</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>73,87%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>20,7%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>23,35%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>11056</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>7857</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>11769</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,94%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>66,76%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>18</t>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10262</t>
+          <t>10136</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>11769</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>11769</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>11769</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>2954</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>2954</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>2954</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>11769</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>11769</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>11769</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4004</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,83%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2751</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6280</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>11,77%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>26,87%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4041</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1426</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7423</t>
+          <t>8407</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>39423</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>36720</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,17%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>20618</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>17089</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>22604</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>17151</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>22591</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>88,23%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>73,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,73%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>39423</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>36683</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,81%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56670</t>
+          <t>55686</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>62667</t>
+          <t>62665</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>23369</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>23369</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>23369</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6677,64 +6677,64 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2213</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3497</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3644</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5805</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2213</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2213</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2213</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3497</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3497</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3497</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5805</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5805</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5805</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2279</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,81%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>39,32%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1344</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3637</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>29,65%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2949</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>27,76%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>80,24%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3658</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>11,84%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>519</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>42,91%</t>
         </is>
       </c>
     </row>
@@ -7020,74 +7020,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5226</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3466</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5795</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,19%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>59,82%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3188</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4532</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>70,35%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3334</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1687</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4615</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>72,24%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>36,55%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>5201</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2239</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5899</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>88,16%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>37,95%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>9</t>
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>8389</t>
+          <t>8561</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>9891</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>10410</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>10410</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>10410</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,107 +7250,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4537</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,18%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>60,51%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4453</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>12,21%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4740</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>7,14%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>53,72%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5157</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>6,82%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2965</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86,82%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>39,54%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>6546</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>6352</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>7277</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>3836</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>8289</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>87,79%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,27 +7438,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>13823</t>
+          <t>12862</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>13850</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>6546</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6546</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>6546</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>13850</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>13850</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>13850</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7706,64 +7706,64 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6746</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2577</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2572</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>7538</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>10115</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>6746</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>6746</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>6746</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2577</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>2577</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2577</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>10115</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>10115</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>10115</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>990</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -8049,74 +8049,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20694</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>16888</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>75,9%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>15807</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>12707</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>92,17%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>74,09%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>15903</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>13129</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>17184</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>92,55%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>76,4%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>22324</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>18213</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>24034</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>92,88%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>75,78%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>51</t>
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>38131</t>
+          <t>36597</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33941</t>
+          <t>32807</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40161</t>
+          <t>38445</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
